--- a/public/assets/template-excel/tiang.xlsx
+++ b/public/assets/template-excel/tiang.xlsx
@@ -11,61 +11,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Nama Area</t>
-  </si>
-  <si>
-    <t>Nama ODP</t>
-  </si>
-  <si>
-    <t>Klasifikasi</t>
-  </si>
-  <si>
-    <t>Jenis Passive Splitter</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Kapasitas Maksimal</t>
-  </si>
-  <si>
-    <t>Kapasitas Terpakai</t>
-  </si>
-  <si>
-    <t>Cutoff Data</t>
-  </si>
-  <si>
-    <t>AM011748</t>
-  </si>
-  <si>
-    <t>asdasd</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>ODP</t>
-  </si>
-  <si>
-    <t>1.674173</t>
-  </si>
-  <si>
-    <t>101.442412</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>CABANG</t>
+  </si>
+  <si>
+    <t>DIAMETER</t>
+  </si>
+  <si>
+    <t>PANJANG</t>
+  </si>
+  <si>
+    <t>WILAYAH</t>
+  </si>
+  <si>
+    <t>KODE</t>
+  </si>
+  <si>
+    <t>LATITUDE</t>
+  </si>
+  <si>
+    <t>LONGITUDE</t>
+  </si>
+  <si>
+    <t>CUT OFF DATA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
-  </numFmts>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -74,43 +50,17 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF000000"/>
+      <sz val="8.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF071437"/>
-      <name val="Inter"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -119,27 +69,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -353,69 +288,31 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="16.13"/>
-    <col customWidth="1" min="4" max="4" width="19.25"/>
-    <col customWidth="1" min="7" max="7" width="17.5"/>
-    <col customWidth="1" min="8" max="8" width="19.0"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4">
-        <v>20.0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>16.0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>45369.0</v>
       </c>
     </row>
   </sheetData>
